--- a/Data_Product/App_Data/BBGNGLGT.xlsx
+++ b/Data_Product/App_Data/BBGNGLGT.xlsx
@@ -5,10 +5,10 @@
   <x:workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ngotrungduong\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PRODUCTDATA1\DATAPRODUCT\Data_Product\App_Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D7A9E229-62EE-4CD5-B21D-3C8FF4F33F5A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CC0CD89-DD6C-49A7-B3AA-E84116D80E4D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <x:bookViews>
     <x:workbookView xWindow="0" yWindow="0" windowWidth="24720" windowHeight="12105" firstSheet="0" activeTab="0" xr2:uid="{51577134-7CEF-4490-9A02-725D1462A1F6}"/>
   </x:bookViews>
@@ -67,16 +67,115 @@
     <x:t>Ghi chú</x:t>
   </x:si>
   <x:si>
+    <x:t>Giờ NM</x:t>
+  </x:si>
+  <x:si>
     <x:t>NM.HRC1</x:t>
   </x:si>
   <x:si>
+    <x:t>Đúc1</x:t>
+  </x:si>
+  <x:si>
     <x:t>NM.HRC2</x:t>
   </x:si>
   <x:si>
+    <x:t>Đúc 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>51</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loại 1</x:t>
+  </x:si>
+  <x:si>
     <x:t/>
   </x:si>
   <x:si>
-    <x:t>GBF251A2999813</x:t>
+    <x:t>07:39</x:t>
+  </x:si>
+  <x:si>
+    <x:t>59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GBF251A3015759</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GBF251A3015751</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08:21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GBF251A3015810</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09:49</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GBF251A3015841</x:t>
+  </x:si>
+  <x:si>
+    <x:t>41</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09:43</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GBF251A3015847</x:t>
+  </x:si>
+  <x:si>
+    <x:t>47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09:02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GBF251A3015923</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12:04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GBF251A3015931</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12:20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GBF251A3015953</x:t>
+  </x:si>
+  <x:si>
+    <x:t>53</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11:13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GBF251A3016026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13:18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GBF251A3016028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13:58</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -86,7 +185,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="0" formatCode=""/>
   </x:numFmts>
-  <x:fonts count="8" x14ac:knownFonts="1">
+  <x:fonts count="10" x14ac:knownFonts="1">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -130,6 +229,20 @@
       <x:family val="1"/>
     </x:font>
     <x:font>
+      <x:sz val="13"/>
+      <x:color theme="1"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:sz val="13"/>
+      <x:color theme="1"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
       <x:color rgb="FF000000"/>
@@ -153,7 +266,7 @@
       <x:patternFill patternType="gray125"/>
     </x:fill>
   </x:fills>
-  <x:borders count="15">
+  <x:borders count="4">
     <x:border>
       <x:left/>
       <x:right/>
@@ -178,144 +291,6 @@
     </x:border>
     <x:border>
       <x:left style="thin">
-        <x:color auto="1"/>
-      </x:left>
-      <x:right/>
-      <x:top style="thin">
-        <x:color auto="1"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color auto="1"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right style="thin">
-        <x:color auto="1"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color auto="1"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color auto="1"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color auto="1"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color auto="1"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color auto="1"/>
-      </x:top>
-      <x:bottom/>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color auto="1"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color auto="1"/>
-      </x:right>
-      <x:top/>
-      <x:bottom style="thin">
-        <x:color auto="1"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color auto="1"/>
-      </x:left>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top style="thin">
-        <x:color auto="1"/>
-      </x:top>
-      <x:bottom/>
-      <x:diagonal/>
-    </x:border>
-    <x:border diagonalUp="0" diagonalDown="0">
-      <x:left style="thin">
-        <x:color rgb="00000000"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FF000000"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="00000000"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="00000000"/>
-      </x:bottom>
-      <x:diagonal style="none">
-        <x:color rgb="FF000000"/>
-      </x:diagonal>
-    </x:border>
-    <x:border diagonalUp="0" diagonalDown="0">
-      <x:left style="thin">
-        <x:color rgb="FF000000"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="00000000"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="00000000"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="00000000"/>
-      </x:bottom>
-      <x:diagonal style="none">
-        <x:color rgb="FF000000"/>
-      </x:diagonal>
-    </x:border>
-    <x:border diagonalUp="0" diagonalDown="0">
-      <x:left style="thin">
-        <x:color rgb="00000000"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="00000000"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="00000000"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FF000000"/>
-      </x:bottom>
-      <x:diagonal style="none">
-        <x:color rgb="FF000000"/>
-      </x:diagonal>
-    </x:border>
-    <x:border diagonalUp="0" diagonalDown="0">
-      <x:left style="thin">
-        <x:color rgb="00000000"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FF000000"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF000000"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FF000000"/>
-      </x:bottom>
-      <x:diagonal style="none">
-        <x:color rgb="FF000000"/>
-      </x:diagonal>
-    </x:border>
-    <x:border diagonalUp="0" diagonalDown="0">
-      <x:left style="thin">
         <x:color rgb="FF000000"/>
       </x:left>
       <x:right style="thin">
@@ -327,46 +302,19 @@
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
-      <x:diagonal style="none">
-        <x:color rgb="FF000000"/>
-      </x:diagonal>
+      <x:diagonal/>
     </x:border>
-    <x:border diagonalUp="0" diagonalDown="0">
-      <x:left style="thin">
-        <x:color rgb="00000000"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="00000000"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF000000"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="00000000"/>
-      </x:bottom>
-      <x:diagonal style="none">
-        <x:color rgb="FF000000"/>
-      </x:diagonal>
-    </x:border>
-    <x:border diagonalUp="0" diagonalDown="0">
+    <x:border>
       <x:left style="thin">
         <x:color rgb="FF000000"/>
       </x:left>
-      <x:right style="thin">
-        <x:color rgb="FF000000"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="00000000"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FF000000"/>
-      </x:bottom>
-      <x:diagonal style="none">
-        <x:color rgb="FF000000"/>
-      </x:diagonal>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="14">
+  <x:cellStyleXfs count="10">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -380,110 +328,71 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="14" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="27">
+  <x:cellXfs count="19">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -838,7 +747,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:Y10"/>
+  <x:dimension ref="A1:AA10"/>
   <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <x:cols>
     <x:col min="1" max="1" width="9.140625" style="0" customWidth="1"/>
@@ -846,214 +755,694 @@
     <x:col min="3" max="3" width="12.140625" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="22.570312" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="23.425781" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="28.570312" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="31.285156" style="0" customWidth="1"/>
     <x:col min="7" max="7" width="27.425781" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="13.710938" style="0" customWidth="1"/>
-    <x:col min="9" max="9" width="12.425781" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="11.570312" style="0" customWidth="1"/>
+    <x:col min="8" max="10" width="13.710938" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="12.425781" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="11.570312" style="0" customWidth="1"/>
+    <x:col min="13" max="14" width="9.140625" style="0" customWidth="1"/>
+    <x:col min="15" max="15" width="10.285156" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:25" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <x:c r="A1" s="1"/>
-      <x:c r="B1" s="1"/>
-      <x:c r="C1" s="1"/>
-      <x:c r="D1" s="1"/>
-      <x:c r="E1" s="1"/>
-      <x:c r="F1" s="1"/>
-    </x:row>
-    <x:row r="2" spans="1:25" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <x:c r="A2" s="1"/>
-      <x:c r="B2" s="1"/>
-      <x:c r="C2" s="1"/>
-      <x:c r="D2" s="1"/>
-      <x:c r="E2" s="1"/>
-      <x:c r="F2" s="1"/>
-    </x:row>
-    <x:row r="4" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <x:c r="E4" s="2" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F4" s="7"/>
-      <x:c r="G4" s="7"/>
-      <x:c r="H4" s="7"/>
-      <x:c r="I4" s="7"/>
-      <x:c r="J4" s="7"/>
-      <x:c r="K4" s="7"/>
-      <x:c r="L4" s="7"/>
-      <x:c r="O4" s="3"/>
-      <x:c r="P4" s="3"/>
-      <x:c r="Q4" s="3"/>
-      <x:c r="R4" s="3"/>
-      <x:c r="S4" s="3"/>
-      <x:c r="T4" s="3"/>
-      <x:c r="U4" s="3"/>
-      <x:c r="V4" s="3"/>
-      <x:c r="W4" s="3"/>
-      <x:c r="X4" s="3"/>
-      <x:c r="Y4" s="3"/>
-    </x:row>
-    <x:row r="5" spans="1:25" x14ac:dyDescent="0.25">
-      <x:c r="A5" s="5" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B5" s="5"/>
-      <x:c r="C5" s="5"/>
-      <x:c r="D5" s="5"/>
-      <x:c r="E5" s="5"/>
-      <x:c r="F5" s="5"/>
-      <x:c r="G5" s="5"/>
-      <x:c r="H5" s="5"/>
-      <x:c r="I5" s="5"/>
-      <x:c r="J5" s="5"/>
-      <x:c r="K5" s="5"/>
-      <x:c r="L5" s="5"/>
-      <x:c r="M5" s="5"/>
-      <x:c r="N5" s="5"/>
-      <x:c r="O5" s="5"/>
-      <x:c r="P5" s="5"/>
-      <x:c r="Q5" s="5"/>
-      <x:c r="R5" s="5"/>
-      <x:c r="S5" s="5"/>
-      <x:c r="T5" s="5"/>
-    </x:row>
-    <x:row r="7" spans="1:25" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <x:c r="A7" s="9" t="s">
+    <x:row r="1" spans="1:27" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <x:c r="A1" s="9"/>
+      <x:c r="B1" s="9"/>
+      <x:c r="C1" s="9"/>
+      <x:c r="D1" s="9"/>
+      <x:c r="E1" s="9"/>
+      <x:c r="F1" s="9"/>
+    </x:row>
+    <x:row r="2" spans="1:27" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <x:c r="A2" s="9"/>
+      <x:c r="B2" s="9"/>
+      <x:c r="C2" s="9"/>
+      <x:c r="D2" s="9"/>
+      <x:c r="E2" s="9"/>
+      <x:c r="F2" s="9"/>
+    </x:row>
+    <x:row r="4" spans="1:27" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <x:c r="E4" s="10" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F4" s="11"/>
+      <x:c r="G4" s="11"/>
+      <x:c r="H4" s="11"/>
+      <x:c r="I4" s="11"/>
+      <x:c r="J4" s="11"/>
+      <x:c r="K4" s="11"/>
+      <x:c r="L4" s="11"/>
+      <x:c r="M4" s="11"/>
+      <x:c r="N4" s="11"/>
+      <x:c r="Q4" s="1"/>
+      <x:c r="R4" s="1"/>
+      <x:c r="S4" s="1"/>
+      <x:c r="T4" s="1"/>
+      <x:c r="U4" s="1"/>
+      <x:c r="V4" s="1"/>
+      <x:c r="W4" s="1"/>
+      <x:c r="X4" s="1"/>
+      <x:c r="Y4" s="1"/>
+      <x:c r="Z4" s="1"/>
+      <x:c r="AA4" s="1"/>
+    </x:row>
+    <x:row r="5" spans="1:27" x14ac:dyDescent="0.25">
+      <x:c r="A5" s="12" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B5" s="12"/>
+      <x:c r="C5" s="12"/>
+      <x:c r="D5" s="12"/>
+      <x:c r="E5" s="12"/>
+      <x:c r="F5" s="12"/>
+      <x:c r="G5" s="12"/>
+      <x:c r="H5" s="12"/>
+      <x:c r="I5" s="12"/>
+      <x:c r="J5" s="12"/>
+      <x:c r="K5" s="12"/>
+      <x:c r="L5" s="12"/>
+      <x:c r="M5" s="12"/>
+      <x:c r="N5" s="12"/>
+      <x:c r="O5" s="12"/>
+      <x:c r="P5" s="12"/>
+      <x:c r="Q5" s="12"/>
+      <x:c r="R5" s="12"/>
+      <x:c r="S5" s="12"/>
+      <x:c r="T5" s="12"/>
+      <x:c r="U5" s="12"/>
+      <x:c r="V5" s="12"/>
+    </x:row>
+    <x:row r="7" spans="1:27" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <x:c r="A7" s="2" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B7" s="9" t="s">
+      <x:c r="B7" s="2" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="9" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D7" s="9" t="s">
+      <x:c r="C7" s="2" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D7" s="2" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="9" t="s">
+      <x:c r="E7" s="2" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="9" t="s">
+      <x:c r="F7" s="2" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="9" t="s">
+      <x:c r="G7" s="2" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="17" t="s">
+      <x:c r="H7" s="4" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="18"/>
-      <x:c r="J7" s="19" t="s">
+      <x:c r="I7" s="4"/>
+      <x:c r="J7" s="4"/>
+      <x:c r="K7" s="4"/>
+      <x:c r="L7" s="4" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="19" t="s">
+      <x:c r="M7" s="4" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="19" t="s">
+      <x:c r="N7" s="4" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="20"/>
-      <x:c r="N7" s="21"/>
-      <x:c r="O7" s="21"/>
-      <x:c r="P7" s="21"/>
-      <x:c r="Q7" s="21"/>
-      <x:c r="R7" s="21"/>
-      <x:c r="S7" s="21"/>
-      <x:c r="T7" s="21"/>
-    </x:row>
-    <x:row r="8" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <x:c r="A8" s="9"/>
-      <x:c r="B8" s="9"/>
-      <x:c r="C8" s="9"/>
-      <x:c r="D8" s="9"/>
-      <x:c r="E8" s="9"/>
-      <x:c r="F8" s="9"/>
-      <x:c r="G8" s="9"/>
-      <x:c r="H8" s="9" t="s">
+      <x:c r="O7" s="4" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="I8" s="9" t="s">
+      <x:c r="P7" s="14"/>
+      <x:c r="Q7" s="14"/>
+      <x:c r="R7" s="14"/>
+      <x:c r="S7" s="14"/>
+      <x:c r="T7" s="14"/>
+      <x:c r="U7" s="5"/>
+      <x:c r="V7" s="5"/>
+    </x:row>
+    <x:row r="8" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <x:c r="A8" s="2"/>
+      <x:c r="B8" s="2"/>
+      <x:c r="C8" s="2"/>
+      <x:c r="D8" s="2"/>
+      <x:c r="E8" s="2"/>
+      <x:c r="F8" s="2"/>
+      <x:c r="G8" s="2"/>
+      <x:c r="H8" s="2" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="J8" s="22"/>
-      <x:c r="K8" s="22"/>
-      <x:c r="L8" s="22"/>
-      <x:c r="M8" s="20"/>
-      <x:c r="N8" s="21"/>
-      <x:c r="O8" s="21"/>
-      <x:c r="P8" s="21"/>
-      <x:c r="Q8" s="21"/>
-      <x:c r="R8" s="21"/>
-      <x:c r="S8" s="21"/>
-      <x:c r="T8" s="21"/>
-    </x:row>
-    <x:row r="9" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <x:c r="A9" s="23">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B9" s="24" t="s">
+      <x:c r="I8" s="2" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J8" s="2" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C9" s="24" t="s">
+      <x:c r="K8" s="2" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="L8" s="4"/>
+      <x:c r="M8" s="4"/>
+      <x:c r="N8" s="4"/>
+      <x:c r="O8" s="4"/>
+      <x:c r="P8" s="14"/>
+      <x:c r="Q8" s="14"/>
+      <x:c r="R8" s="14"/>
+      <x:c r="S8" s="14"/>
+      <x:c r="T8" s="14"/>
+      <x:c r="U8" s="5"/>
+      <x:c r="V8" s="5"/>
+    </x:row>
+    <x:row r="9" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <x:c r="A9" s="4">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C9" s="6" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D9" s="6">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E9" s="6">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F9" s="6">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D9" s="24">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E9" s="24">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F9" s="24">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="24">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H9" s="24">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I9" s="24">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J9" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="K9" s="24"/>
-      <x:c r="L9" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="M9" s="25"/>
-      <x:c r="N9" s="21"/>
-      <x:c r="O9" s="21"/>
-      <x:c r="P9" s="21"/>
-      <x:c r="Q9" s="21"/>
-      <x:c r="R9" s="21"/>
-      <x:c r="S9" s="21"/>
-      <x:c r="T9" s="21"/>
-    </x:row>
-    <x:row r="10" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <x:c r="A10" s="26"/>
-      <x:c r="B10" s="26"/>
-      <x:c r="C10" s="26"/>
-      <x:c r="D10" s="26"/>
-      <x:c r="E10" s="26"/>
-      <x:c r="F10" s="26"/>
-      <x:c r="G10" s="26"/>
-      <x:c r="H10" s="26"/>
-      <x:c r="I10" s="26"/>
-      <x:c r="J10" s="26"/>
-      <x:c r="K10" s="26"/>
-      <x:c r="L10" s="26"/>
-      <x:c r="M10" s="26"/>
+      <x:c r="G9" s="6">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H9" s="6">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I9" s="6">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J9" s="6">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K9" s="6">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L9" s="6" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M9" s="6" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="N9" s="6" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="O9" s="6" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="P9" s="14"/>
+      <x:c r="Q9" s="14"/>
+      <x:c r="R9" s="14"/>
+      <x:c r="S9" s="14"/>
+      <x:c r="T9" s="14"/>
+      <x:c r="U9" s="5"/>
+      <x:c r="V9" s="5"/>
+    </x:row>
+    <x:row r="10" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <x:c r="A10" s="15">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B10" s="16" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C10" s="16" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D10" s="16">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E10" s="16">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F10" s="16">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G10" s="16">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J10" s="16">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K10" s="16">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L10" s="16" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M10" s="16" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="N10" s="16" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="O10" s="16" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="P10" s="14"/>
+      <x:c r="Q10" s="14"/>
+      <x:c r="R10" s="14"/>
+      <x:c r="S10" s="14"/>
+      <x:c r="T10" s="14"/>
+    </x:row>
+    <x:row r="11" spans="1:27">
+      <x:c r="A11" s="17">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B11" s="18" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C11" s="18" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D11" s="18">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E11" s="18">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F11" s="18">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G11" s="18">
+        <x:v>-2</x:v>
+      </x:c>
+      <x:c r="H11" s="18">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I11" s="18">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J11" s="18">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K11" s="18">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L11" s="18" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M11" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="N11" s="18" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="O11" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="P11" s="14"/>
+      <x:c r="Q11" s="14"/>
+      <x:c r="R11" s="14"/>
+      <x:c r="S11" s="14"/>
+      <x:c r="T11" s="14"/>
+    </x:row>
+    <x:row r="12" spans="1:27">
+      <x:c r="A12" s="17">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B12" s="18" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C12" s="18" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D12" s="18">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E12" s="18">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F12" s="18">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G12" s="18">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H12" s="18">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I12" s="18">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J12" s="18">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K12" s="18">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L12" s="18" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M12" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="N12" s="18" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="O12" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="P12" s="14"/>
+      <x:c r="Q12" s="14"/>
+      <x:c r="R12" s="14"/>
+      <x:c r="S12" s="14"/>
+      <x:c r="T12" s="14"/>
+    </x:row>
+    <x:row r="13" spans="1:27">
+      <x:c r="A13" s="17">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B13" s="18" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C13" s="18" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D13" s="18">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E13" s="18">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F13" s="18">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G13" s="18">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H13" s="18">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I13" s="18">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J13" s="18">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K13" s="18">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L13" s="18" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M13" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="N13" s="18" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="O13" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="P13" s="14"/>
+      <x:c r="Q13" s="14"/>
+      <x:c r="R13" s="14"/>
+      <x:c r="S13" s="14"/>
+      <x:c r="T13" s="14"/>
+    </x:row>
+    <x:row r="14" spans="1:27">
+      <x:c r="A14" s="17">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B14" s="18" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C14" s="18" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D14" s="18">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E14" s="18">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F14" s="18">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G14" s="18">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H14" s="18">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I14" s="18">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J14" s="18">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K14" s="18">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L14" s="18" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M14" s="18" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="N14" s="18" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="O14" s="18" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="P14" s="14"/>
+      <x:c r="Q14" s="14"/>
+      <x:c r="R14" s="14"/>
+      <x:c r="S14" s="14"/>
+      <x:c r="T14" s="14"/>
+    </x:row>
+    <x:row r="15" spans="1:27">
+      <x:c r="A15" s="17">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B15" s="18" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C15" s="18" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D15" s="18">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E15" s="18">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F15" s="18">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G15" s="18">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H15" s="18">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I15" s="18">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J15" s="18">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K15" s="18">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L15" s="18" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M15" s="18" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="N15" s="18" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="O15" s="18" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="P15" s="14"/>
+      <x:c r="Q15" s="14"/>
+      <x:c r="R15" s="14"/>
+      <x:c r="S15" s="14"/>
+      <x:c r="T15" s="14"/>
+    </x:row>
+    <x:row r="16" spans="1:27">
+      <x:c r="A16" s="17">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B16" s="18" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C16" s="18" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D16" s="18">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E16" s="18">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F16" s="18">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G16" s="18">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H16" s="18">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I16" s="18">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J16" s="18">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K16" s="18">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L16" s="18" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M16" s="18" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="N16" s="18" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="O16" s="18" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="P16" s="14"/>
+      <x:c r="Q16" s="14"/>
+      <x:c r="R16" s="14"/>
+      <x:c r="S16" s="14"/>
+      <x:c r="T16" s="14"/>
+    </x:row>
+    <x:row r="17" spans="1:27">
+      <x:c r="A17" s="17">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B17" s="18" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C17" s="18" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D17" s="18">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E17" s="18">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F17" s="18">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G17" s="18">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H17" s="18">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I17" s="18">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J17" s="18">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K17" s="18">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L17" s="18" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M17" s="18" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N17" s="18" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="O17" s="18" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="P17" s="14"/>
+      <x:c r="Q17" s="14"/>
+      <x:c r="R17" s="14"/>
+      <x:c r="S17" s="14"/>
+      <x:c r="T17" s="14"/>
+    </x:row>
+    <x:row r="18" spans="1:27">
+      <x:c r="A18" s="17">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B18" s="18" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C18" s="18" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D18" s="18">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E18" s="18">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F18" s="18">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G18" s="18">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H18" s="18">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I18" s="18">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J18" s="18">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K18" s="18">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L18" s="18" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M18" s="18" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="N18" s="18" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="O18" s="18" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="P18" s="14"/>
+      <x:c r="Q18" s="14"/>
+      <x:c r="R18" s="14"/>
+      <x:c r="S18" s="14"/>
+      <x:c r="T18" s="14"/>
     </x:row>
   </x:sheetData>
-  <x:mergeCells count="7">
+  <x:mergeCells count="8">
     <x:mergeCell ref="A1:F2"/>
-    <x:mergeCell ref="E4:L4"/>
-    <x:mergeCell ref="A5:T5"/>
-    <x:mergeCell ref="H7:I7"/>
-    <x:mergeCell ref="J7:J8"/>
-    <x:mergeCell ref="K7:K8"/>
+    <x:mergeCell ref="E4:N4"/>
+    <x:mergeCell ref="A5:V5"/>
+    <x:mergeCell ref="H7:K7"/>
     <x:mergeCell ref="L7:L8"/>
+    <x:mergeCell ref="M7:M8"/>
+    <x:mergeCell ref="N7:N8"/>
+    <x:mergeCell ref="O7:O8"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
